--- a/docs/v1.4/EIDE-GAP-35_Ra_soat_ma_v1.4.xlsx
+++ b/docs/v1.4/EIDE-GAP-35_Ra_soat_ma_v1.4.xlsx
@@ -92,12 +92,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F8CBAD"/>
+        <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
+        <fgColor rgb="00F8CBAD"/>
       </patternFill>
     </fill>
     <fill>
@@ -217,10 +217,10 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -837,12 +837,12 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>XONG Đ1</t>
+          <t>XONG Đ1 / XONG Đ2</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Đã hiện thực ngày 24/09/2026; cột cuối ghi tệp và BÀI KIỂM canh nó. `make check-py` xanh: ruff, 1975 test, check-spec, check-gen.</t>
+          <t>Đã hiện thực ngày 24/09/2026; cột cuối ghi tệp và BÀI KIỂM canh nó. `make check-py` xanh: ruff, 2011 test, check-spec, check-gen.</t>
         </is>
       </c>
     </row>
@@ -1775,9 +1775,9 @@
           <t>S0 quét mẫu chèn lệnh trong DỮ LIỆU ("ignore previous instructions", lệnh shell) → đánh dấu tài liệu nghi ngờ, cảnh báo, không thực thi, ghi sổ</t>
         </is>
       </c>
-      <c r="E14" s="10" t="inlineStr">
-        <is>
-          <t>KHÔNG</t>
+      <c r="E14" s="9" t="inlineStr">
+        <is>
+          <t>XONG Đ2</t>
         </is>
       </c>
       <c r="F14" s="7" t="inlineStr">
@@ -1811,7 +1811,11 @@
         </is>
       </c>
       <c r="L14" s="7" t="inlineStr"/>
-      <c r="M14" s="7" t="inlineStr"/>
+      <c r="M14" s="7" t="inlineStr">
+        <is>
+          <t>src/eide_core/inject_scan.py (mới) — 8 mẫu P-INJ, lọc theo DÒNG (không bỏ cả đoạn: bỏ cả đoạn cho phép kẻ tấn công xoá tri thức của tệp bằng một dòng, [DEV-236]); nối vào ingest.index_text, đoạn nghi KHÔNG vào chỉ mục và được báo qua `suspect[]`. Canh bởi tests/test_classify_v14.py::test_doan_chen_lenh_bi_loai_khoi_chi_muc, ::test_loc_theo_dong_giu_phan_ky_thuat, ::test_khong_bao_dong_gia_tren_van_ban_ky_thuat</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
@@ -1834,7 +1838,7 @@
           <t>Ở ASK/REJECT/STOP lượt kết thúc tại S0, không lời gọi mô hình nào; mục tiêu &lt; 300 ms</t>
         </is>
       </c>
-      <c r="E15" s="11" t="inlineStr">
+      <c r="E15" s="10" t="inlineStr">
         <is>
           <t>CÓ</t>
         </is>
@@ -1897,7 +1901,7 @@
           <t>S1a tách câu thành ba kênh DIRECTIVE / PRODUCT / DATA bằng một lời gọi mô hình nhỏ có lược đồ; req.elicit CHỈ nhận product_text</t>
         </is>
       </c>
-      <c r="E16" s="10" t="inlineStr">
+      <c r="E16" s="11" t="inlineStr">
         <is>
           <t>KHÔNG</t>
         </is>
@@ -1956,7 +1960,7 @@
           <t>Rủi ro tác tử tự phát hiện đi vào risk[] của đặc tả, KHÔNG BAO GIỜ thành FR</t>
         </is>
       </c>
-      <c r="E17" s="10" t="inlineStr">
+      <c r="E17" s="11" t="inlineStr">
         <is>
           <t>KHÔNG</t>
         </is>
@@ -2267,7 +2271,7 @@
           <t>Hiệu chuẩn confidence theo tập kịch bản (bảng điểm thô → xác suất đúng thực đo), ngưỡng 0,60/0,85 đặt ở mức sai &lt; 5 % và &lt; 20 %</t>
         </is>
       </c>
-      <c r="E22" s="10" t="inlineStr">
+      <c r="E22" s="11" t="inlineStr">
         <is>
           <t>KHÔNG</t>
         </is>
@@ -2566,7 +2570,7 @@
           <t>Cổng an toàn (G-OPS) KHÔNG BAO GIỜ là một mục trong thẻ S3 — thẻ riêng do Policy engine phát</t>
         </is>
       </c>
-      <c r="E27" s="11" t="inlineStr">
+      <c r="E27" s="10" t="inlineStr">
         <is>
           <t>CÓ</t>
         </is>
@@ -2625,7 +2629,7 @@
           <t>Hai nút cùng cần một tiền đề chỉ sinh MỘT gap (gộp khoá trùng trước khi gọi mô hình)</t>
         </is>
       </c>
-      <c r="E28" s="10" t="inlineStr">
+      <c r="E28" s="11" t="inlineStr">
         <is>
           <t>KHÔNG</t>
         </is>
@@ -2684,7 +2688,7 @@
           <t>S2 dựng bảng Inventory xác định (project, requirements, options, passports, documents, design, code, toolchain, sim, target, runs, adrs, assumptions) — 0 token, &lt; 50 ms, cache theo mtime</t>
         </is>
       </c>
-      <c r="E29" s="10" t="inlineStr">
+      <c r="E29" s="11" t="inlineStr">
         <is>
           <t>KHÔNG</t>
         </is>
@@ -2810,7 +2814,7 @@
           <t>Planner đối chiếu requires với Inventory ∪ produces của các nút trước; thiếu + có how_to_get → chèn nút (đệ quy ≤ 3, phát hiện vòng)</t>
         </is>
       </c>
-      <c r="E31" s="10" t="inlineStr">
+      <c r="E31" s="11" t="inlineStr">
         <is>
           <t>KHÔNG</t>
         </is>
@@ -2869,7 +2873,7 @@
           <t>Thiếu artefact KHÔNG có how_to_get (đường dẫn, mã chip) → tạo gap cho S3, không chạy nút</t>
         </is>
       </c>
-      <c r="E32" s="10" t="inlineStr">
+      <c r="E32" s="11" t="inlineStr">
         <is>
           <t>KHÔNG</t>
         </is>
@@ -2991,7 +2995,7 @@
           <t>Router kiểm requires lần nữa trên Inventory tươi TRƯỚC khi chạy và kiểm produces (hiện vật có thật, đúng lược đồ) SAU khi chạy</t>
         </is>
       </c>
-      <c r="E34" s="10" t="inlineStr">
+      <c r="E34" s="11" t="inlineStr">
         <is>
           <t>KHÔNG</t>
         </is>
@@ -3050,7 +3054,7 @@
           <t>Nút hỏng E2xxx (thiếu tiền đề) lúc chạy → quay về S3 với gap tương ứng (≤ 2 lần/lượt), không chết tại chỗ</t>
         </is>
       </c>
-      <c r="E35" s="10" t="inlineStr">
+      <c r="E35" s="11" t="inlineStr">
         <is>
           <t>KHÔNG</t>
         </is>
@@ -4022,7 +4026,7 @@
           <t>Registry chip trong SQLite (640 hạt giống từ SVD/ATDF): code, họ, ISA, gói, bí danh, URL nhà sản xuất</t>
         </is>
       </c>
-      <c r="E51" s="10" t="inlineStr">
+      <c r="E51" s="11" t="inlineStr">
         <is>
           <t>KHÔNG</t>
         </is>
@@ -4443,7 +4447,7 @@
           <t>fact.compare(a, b, rule) → {verdict, severity, evidence[2 trích dẫn], unverified}; vế ĐỒNG → unverified, severity hạ thành info, planner không dùng làm điều kiện tự động</t>
         </is>
       </c>
-      <c r="E58" s="10" t="inlineStr">
+      <c r="E58" s="11" t="inlineStr">
         <is>
           <t>KHÔNG</t>
         </is>
@@ -4502,7 +4506,7 @@
           <t>Constant-guard: sau mỗi nút sinh mã, quét hằng số điện/thời gian (kèm đơn vị hoặc macro F_CPU/BAUD/I2C_SPEED) và đối chiếu kho Fact; không truy vết được → nút không sạch</t>
         </is>
       </c>
-      <c r="E59" s="11" t="inlineStr">
+      <c r="E59" s="10" t="inlineStr">
         <is>
           <t>CÓ</t>
         </is>
@@ -4746,7 +4750,7 @@
           <t>Cache kết quả parse/clarify theo hash(câu chuẩn hoá + inventory hash) trong 10 phút — để chạy lặp kịch bản rẻ và tất định hơn</t>
         </is>
       </c>
-      <c r="E63" s="10" t="inlineStr">
+      <c r="E63" s="11" t="inlineStr">
         <is>
           <t>KHÔNG</t>
         </is>
@@ -4864,7 +4868,7 @@
           <t>Kế toán mỗi lời gọi {role, model, tokens_in/out, seconds, usd} vào sổ cái; S6 tổng hợp</t>
         </is>
       </c>
-      <c r="E65" s="11" t="inlineStr">
+      <c r="E65" s="10" t="inlineStr">
         <is>
           <t>CÓ</t>
         </is>
@@ -5104,7 +5108,7 @@
           <t>Mọi lệnh chạy qua sandbox: thư mục cho phép, không mạng mặc định (bật theo nút khai network=true), giới hạn CPU/RAM/thời gian, môi trường sạch</t>
         </is>
       </c>
-      <c r="E69" s="11" t="inlineStr">
+      <c r="E69" s="10" t="inlineStr">
         <is>
           <t>CÓ</t>
         </is>
@@ -5163,9 +5167,9 @@
           <t>Script người đưa vào được ingest.classify nhận là "script", quét tĩnh (lệnh phá hoại, đọc khoá riêng) → ASK kèm trích dòng nguy hiểm; chạy vẫn trong sandbox</t>
         </is>
       </c>
-      <c r="E70" s="10" t="inlineStr">
-        <is>
-          <t>KHÔNG</t>
+      <c r="E70" s="9" t="inlineStr">
+        <is>
+          <t>XONG Đ2</t>
         </is>
       </c>
       <c r="F70" s="7" t="inlineStr">
@@ -5203,7 +5207,11 @@
           <t>An toàn phải do THIẾT KẾ: ca này đang đạt nhờ tai nạn (brief §6).</t>
         </is>
       </c>
-      <c r="M70" s="7" t="inlineStr"/>
+      <c r="M70" s="7" t="inlineStr">
+        <is>
+          <t>src/eide_core/script_scan.py (mới) — 12 mẫu (rm từ gốc, dd, mkfs, đọc ~/.ssh, curl|sh, exfil, sudo, eval/base64) + cờ `co_the_con_thieu`; ingest.classify quét ngay tại cửa nạp và trả `can_xac_nhan` + trích dòng. TÊN cổng chưa đặt ([DEV-235]: một chữ "G-WL" trong hợp đồng làm chính ingest.classify bị cổng R4 chặn). Canh bởi ::test_script_bi_quet_tinh_va_phai_hoi, ::test_canh_bao_trich_dung_dong_lenh, ::test_script_lanh_khong_bat_canh_bao</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="7" t="inlineStr">
@@ -5285,7 +5293,7 @@
           <t>Manifest ISA đủ họ: armv6-m, armv7-m, armv7e-m, armv8-m, avr8, rv32imac, xtensa-lx6/lx7</t>
         </is>
       </c>
-      <c r="E72" s="10" t="inlineStr">
+      <c r="E72" s="11" t="inlineStr">
         <is>
           <t>KHÔNG</t>
         </is>
@@ -5470,7 +5478,7 @@
           <t>sim.define_criteria sinh criteria.yaml {assert: [uart_contains, gpio_toggles, timing_within, no_hardfault], timeout_s} TRƯỚC khi chạy; đổi sau → G-QUAL</t>
         </is>
       </c>
-      <c r="E75" s="10" t="inlineStr">
+      <c r="E75" s="11" t="inlineStr">
         <is>
           <t>KHÔNG</t>
         </is>
@@ -5647,7 +5655,7 @@
           <t>target.flash: thẻ tóm tắt "nạp gì (hash, kích thước) vào đâu (chip, địa chỉ)" → xác nhận → nạp → verify đọc lại; rút cáp giữa chừng → báo trạng thái không nhất quán + hướng khôi phục</t>
         </is>
       </c>
-      <c r="E78" s="10" t="inlineStr">
+      <c r="E78" s="11" t="inlineStr">
         <is>
           <t>KHÔNG</t>
         </is>
@@ -5765,7 +5773,7 @@
           <t>Một cửa vào: lõi chỉ nhận thao tác của người qua console.act mang HumanAct; RPC khác là máy–máy và bị từ chối E_PROTO_CHANNEL nếu mang hành động</t>
         </is>
       </c>
-      <c r="E80" s="10" t="inlineStr">
+      <c r="E80" s="11" t="inlineStr">
         <is>
           <t>KHÔNG</t>
         </is>
@@ -5946,7 +5954,7 @@
           <t>Envelope {v, id, seq, ts, session, run_id, kind, payload}; hai bộ đếm seq theo chiều; idempotent theo id; mất kết nối → resume(last_seq_seen) phát lại phần thiếu</t>
         </is>
       </c>
-      <c r="E83" s="10" t="inlineStr">
+      <c r="E83" s="11" t="inlineStr">
         <is>
           <t>KHÔNG</t>
         </is>
@@ -6068,7 +6076,7 @@
           <t>11 loại HumanAct: say, choose, decide, confirm, edit, upload, stop, undo, resume, attend, set</t>
         </is>
       </c>
-      <c r="E85" s="10" t="inlineStr">
+      <c r="E85" s="11" t="inlineStr">
         <is>
           <t>KHÔNG</t>
         </is>
@@ -6127,7 +6135,7 @@
           <t>14 UICommand: console.post/stream, card.resolve/expire, surface.set/patch/append/focus/highlight/lock/unlock, run.update, notice, ui.set</t>
         </is>
       </c>
-      <c r="E86" s="10" t="inlineStr">
+      <c r="E86" s="11" t="inlineStr">
         <is>
           <t>KHÔNG</t>
         </is>
@@ -6308,7 +6316,7 @@
           <t>12 ca tuân thủ UP01–UP12 + bộ lint giao thức chạy trong CI cho cả hai phía</t>
         </is>
       </c>
-      <c r="E89" s="10" t="inlineStr">
+      <c r="E89" s="11" t="inlineStr">
         <is>
           <t>KHÔNG</t>
         </is>
@@ -6489,7 +6497,7 @@
           <t>Tất định: cùng câu + cùng store → cùng DX, S0, S2, S4 (100 %); S1/S3 ≥ 90 % cùng intent/gaps qua 5 lần</t>
         </is>
       </c>
-      <c r="E92" s="10" t="inlineStr">
+      <c r="E92" s="11" t="inlineStr">
         <is>
           <t>KHÔNG</t>
         </is>
@@ -7766,7 +7774,7 @@
           <t>DX §2.2 — trích paths/chips/numbers/urls/ids/back_refs/quoted, 0 token</t>
         </is>
       </c>
-      <c r="D2" s="10" t="inlineStr">
+      <c r="D2" s="11" t="inlineStr">
         <is>
           <t>KHÔNG</t>
         </is>
@@ -7808,7 +7816,7 @@
           <t>S1a §2.4 — tách DIRECTIVE/PRODUCT/DATA</t>
         </is>
       </c>
-      <c r="D3" s="10" t="inlineStr">
+      <c r="D3" s="11" t="inlineStr">
         <is>
           <t>KHÔNG</t>
         </is>
@@ -7850,14 +7858,14 @@
           <t>Magic bytes + đuôi → archive|netlist|source|script|log|capture|pdf|image|unknown; mỗi loại một bộ đọc; lỗi đúng lý do</t>
         </is>
       </c>
-      <c r="D4" s="8" t="inlineStr">
-        <is>
-          <t>MỘT PHẦN</t>
+      <c r="D4" s="9" t="inlineStr">
+        <is>
+          <t>XONG Đ2</t>
         </is>
       </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
-          <t>src/eide/caps/archive.py:114 (có magic bytes, câu lỗi đã sửa DEV-210); thiếu script/log/capture và chưa chặn archive.list</t>
+          <t>XONG 24/09: family theo 9 họ + script/log/capture + KHONG_HO_TRO (Altium…) + archive.list là cửa một chiều — src/eide/caps/archive.py::ho_tep, list_, _khong_phai_kho_nen</t>
         </is>
       </c>
       <c r="F4" s="7" t="inlineStr">
@@ -7892,7 +7900,7 @@
           <t>Từ chips[] → thẻ đề nghị 3 lựa chọn; nút không cần Fact vẫn chạy; nút cần Fact đánh dấu chờ</t>
         </is>
       </c>
-      <c r="D5" s="10" t="inlineStr">
+      <c r="D5" s="11" t="inlineStr">
         <is>
           <t>KHÔNG</t>
         </is>
@@ -8060,7 +8068,7 @@
           <t>S4 §3.2 — planner có tiền đề</t>
         </is>
       </c>
-      <c r="D9" s="10" t="inlineStr">
+      <c r="D9" s="11" t="inlineStr">
         <is>
           <t>KHÔNG</t>
         </is>
@@ -8144,7 +8152,7 @@
           <t>Tiêu chí chấp nhận nêu TRƯỚC khi chạy; đổi tiêu chí qua G-QUAL</t>
         </is>
       </c>
-      <c r="D11" s="10" t="inlineStr">
+      <c r="D11" s="11" t="inlineStr">
         <is>
           <t>KHÔNG</t>
         </is>
@@ -8186,7 +8194,7 @@
           <t>Hợp nhất slot theo ưu tiên DX &gt; S3 &gt; mô hình &gt; fill_defaults</t>
         </is>
       </c>
-      <c r="D12" s="10" t="inlineStr">
+      <c r="D12" s="11" t="inlineStr">
         <is>
           <t>KHÔNG</t>
         </is>
@@ -8228,7 +8236,7 @@
           <t>Bảng kiểm kê xác định</t>
         </is>
       </c>
-      <c r="D13" s="10" t="inlineStr">
+      <c r="D13" s="11" t="inlineStr">
         <is>
           <t>KHÔNG</t>
         </is>
@@ -8353,7 +8361,7 @@
           <t>raw, normalized, no_accent, clauses[]</t>
         </is>
       </c>
-      <c r="E2" s="10" t="inlineStr">
+      <c r="E2" s="11" t="inlineStr">
         <is>
           <t>KHÔNG</t>
         </is>
@@ -8390,7 +8398,7 @@
           <t>paths[] (MẢNG), chips[], numbers[], urls[], ids[], back_refs[], quoted[]</t>
         </is>
       </c>
-      <c r="E3" s="10" t="inlineStr">
+      <c r="E3" s="11" t="inlineStr">
         <is>
           <t>KHÔNG</t>
         </is>
@@ -8427,7 +8435,7 @@
           <t>decision, rule_ids[], message</t>
         </is>
       </c>
-      <c r="E4" s="10" t="inlineStr">
+      <c r="E4" s="11" t="inlineStr">
         <is>
           <t>KHÔNG</t>
         </is>
@@ -8464,7 +8472,7 @@
           <t>clauses[{id,text,channel}], product_text, directive_text</t>
         </is>
       </c>
-      <c r="E5" s="10" t="inlineStr">
+      <c r="E5" s="11" t="inlineStr">
         <is>
           <t>KHÔNG</t>
         </is>
@@ -8538,7 +8546,7 @@
           <t>§3.1 — 13 nhóm trường</t>
         </is>
       </c>
-      <c r="E7" s="10" t="inlineStr">
+      <c r="E7" s="11" t="inlineStr">
         <is>
           <t>KHÔNG</t>
         </is>
@@ -8723,7 +8731,7 @@
           <t>ns.part@semver, isa, docs[], facts[]</t>
         </is>
       </c>
-      <c r="E12" s="11" t="inlineStr">
+      <c r="E12" s="10" t="inlineStr">
         <is>
           <t>CÓ</t>
         </is>
@@ -8797,7 +8805,7 @@
           <t>§9.3 / UIP-34 §6 — 6 loại thẻ</t>
         </is>
       </c>
-      <c r="E14" s="10" t="inlineStr">
+      <c r="E14" s="11" t="inlineStr">
         <is>
           <t>KHÔNG</t>
         </is>
@@ -8834,7 +8842,7 @@
           <t>assert[], timeout_s; stimuli[]</t>
         </is>
       </c>
-      <c r="E15" s="10" t="inlineStr">
+      <c r="E15" s="11" t="inlineStr">
         <is>
           <t>KHÔNG</t>
         </is>
@@ -8871,7 +8879,7 @@
           <t>Envelope, HumanAct, UICommand, SurfaceModel/Block, Card, ui.status</t>
         </is>
       </c>
-      <c r="E16" s="10" t="inlineStr">
+      <c r="E16" s="11" t="inlineStr">
         <is>
           <t>KHÔNG</t>
         </is>
@@ -8963,7 +8971,7 @@
           <t>I1 — một cửa vào console.act (HumanAct)</t>
         </is>
       </c>
-      <c r="C2" s="10" t="inlineStr">
+      <c r="C2" s="11" t="inlineStr">
         <is>
           <t>KHÔNG</t>
         </is>
@@ -9059,7 +9067,7 @@
           <t>I4 — lõi không thấy sự kiện chuột/phím</t>
         </is>
       </c>
-      <c r="C5" s="11" t="inlineStr">
+      <c r="C5" s="10" t="inlineStr">
         <is>
           <t>CÓ</t>
         </is>
@@ -9091,7 +9099,7 @@
           <t>I5 — có thứ tự, không trùng, khôi phục được (seq, id, resume)</t>
         </is>
       </c>
-      <c r="C6" s="10" t="inlineStr">
+      <c r="C6" s="11" t="inlineStr">
         <is>
           <t>KHÔNG</t>
         </is>
@@ -9251,7 +9259,7 @@
           <t>confirm (Fact / nguồn)</t>
         </is>
       </c>
-      <c r="C11" s="10" t="inlineStr">
+      <c r="C11" s="11" t="inlineStr">
         <is>
           <t>KHÔNG</t>
         </is>
@@ -9347,7 +9355,7 @@
           <t>stop</t>
         </is>
       </c>
-      <c r="C14" s="11" t="inlineStr">
+      <c r="C14" s="10" t="inlineStr">
         <is>
           <t>CÓ</t>
         </is>
@@ -9443,7 +9451,7 @@
           <t>attend (chuyển tab / chọn hiện vật)</t>
         </is>
       </c>
-      <c r="C17" s="10" t="inlineStr">
+      <c r="C17" s="11" t="inlineStr">
         <is>
           <t>KHÔNG</t>
         </is>
@@ -9539,7 +9547,7 @@
           <t>card.resolve / card.expire</t>
         </is>
       </c>
-      <c r="C20" s="10" t="inlineStr">
+      <c r="C20" s="11" t="inlineStr">
         <is>
           <t>KHÔNG</t>
         </is>
@@ -9571,7 +9579,7 @@
           <t>surface.set / patch / append</t>
         </is>
       </c>
-      <c r="C21" s="10" t="inlineStr">
+      <c r="C21" s="11" t="inlineStr">
         <is>
           <t>KHÔNG</t>
         </is>
@@ -9603,7 +9611,7 @@
           <t>surface.focus / highlight</t>
         </is>
       </c>
-      <c r="C22" s="10" t="inlineStr">
+      <c r="C22" s="11" t="inlineStr">
         <is>
           <t>KHÔNG</t>
         </is>
@@ -9731,7 +9739,7 @@
           <t>ui.set</t>
         </is>
       </c>
-      <c r="C26" s="10" t="inlineStr">
+      <c r="C26" s="11" t="inlineStr">
         <is>
           <t>KHÔNG</t>
         </is>
@@ -9827,7 +9835,7 @@
           <t>UP01–UP12 + lint giao thức trong CI</t>
         </is>
       </c>
-      <c r="C29" s="10" t="inlineStr">
+      <c r="C29" s="11" t="inlineStr">
         <is>
           <t>KHÔNG</t>
         </is>
@@ -10020,7 +10028,7 @@
           <t>ASK</t>
         </is>
       </c>
-      <c r="E4" s="10" t="inlineStr">
+      <c r="E4" s="11" t="inlineStr">
         <is>
           <t>KHÔNG</t>
         </is>
@@ -10062,7 +10070,7 @@
           <t>ASK lần đầu, AUTO cùng gói/nguồn nếu người chọn "tin"</t>
         </is>
       </c>
-      <c r="E5" s="11" t="inlineStr">
+      <c r="E5" s="10" t="inlineStr">
         <is>
           <t>CÓ</t>
         </is>
@@ -10188,7 +10196,7 @@
           <t>Luôn hỏi, thẻ riêng, nêu hậu quả; KHÔNG AUTO ở mọi mức A0–A4</t>
         </is>
       </c>
-      <c r="E8" s="11" t="inlineStr">
+      <c r="E8" s="10" t="inlineStr">
         <is>
           <t>CÓ</t>
         </is>
@@ -13950,7 +13958,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B41"/>
+  <dimension ref="A1:B42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -14032,329 +14040,340 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="27" t="inlineStr"/>
-      <c r="B8" s="19" t="n"/>
+      <c r="A8" s="26" t="inlineStr">
+        <is>
+          <t>XONG Đ2 (đã sửa 24/09/2026)</t>
+        </is>
+      </c>
+      <c r="B8" s="19">
+        <f>COUNTIF('Ra soat (GAP)'!E2:E96,"XONG Đ2")</f>
+        <v/>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="25" t="inlineStr">
+      <c r="A9" s="27" t="inlineStr"/>
+      <c r="B9" s="19" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="25" t="inlineStr">
         <is>
           <t>THEO ĐỢT</t>
         </is>
       </c>
-      <c r="B9" s="19" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="26" t="inlineStr">
+      <c r="B10" s="19" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="26" t="inlineStr">
         <is>
           <t>Đợt 1</t>
         </is>
       </c>
-      <c r="B10" s="19">
+      <c r="B11" s="19">
         <f>COUNTIF('Ra soat (GAP)'!J2:J96,"Đợt 1")</f>
         <v/>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="26" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="26" t="inlineStr">
         <is>
           <t>Đợt 2</t>
         </is>
       </c>
-      <c r="B11" s="19">
+      <c r="B12" s="19">
         <f>COUNTIF('Ra soat (GAP)'!J2:J96,"Đợt 2")</f>
         <v/>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="26" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="26" t="inlineStr">
         <is>
           <t>Đợt 3</t>
         </is>
       </c>
-      <c r="B12" s="19">
+      <c r="B13" s="19">
         <f>COUNTIF('Ra soat (GAP)'!J2:J96,"Đợt 3")</f>
         <v/>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="26" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="26" t="inlineStr">
         <is>
           <t>Đợt 4</t>
         </is>
       </c>
-      <c r="B13" s="19">
+      <c r="B14" s="19">
         <f>COUNTIF('Ra soat (GAP)'!J2:J96,"Đợt 4")</f>
         <v/>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="27" t="inlineStr"/>
-      <c r="B14" s="19" t="n"/>
-    </row>
     <row r="15">
-      <c r="A15" s="25" t="inlineStr">
+      <c r="A15" s="27" t="inlineStr"/>
+      <c r="B15" s="19" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="25" t="inlineStr">
         <is>
           <t>THEO SỬA ĐỔI (Đợt 1)</t>
         </is>
       </c>
-      <c r="B15" s="19" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="26" t="inlineStr">
+      <c r="B16" s="19" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="26" t="inlineStr">
         <is>
           <t>Mục có liên quan Đ1</t>
         </is>
       </c>
-      <c r="B16" s="19">
+      <c r="B17" s="19">
         <f>COUNTIF('Ra soat (GAP)'!I2:I96,"*Đ1*")</f>
         <v/>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="26" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="26" t="inlineStr">
         <is>
           <t>Mục có liên quan Đ2</t>
         </is>
       </c>
-      <c r="B17" s="19">
+      <c r="B18" s="19">
         <f>COUNTIF('Ra soat (GAP)'!I2:I96,"*Đ2*")</f>
         <v/>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="26" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="26" t="inlineStr">
         <is>
           <t>Mục có liên quan Đ3</t>
         </is>
       </c>
-      <c r="B18" s="19">
+      <c r="B19" s="19">
         <f>COUNTIF('Ra soat (GAP)'!I2:I96,"*Đ3*")</f>
         <v/>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="26" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="26" t="inlineStr">
         <is>
           <t>Mục có liên quan Đ4</t>
         </is>
       </c>
-      <c r="B19" s="19">
+      <c r="B20" s="19">
         <f>COUNTIF('Ra soat (GAP)'!I2:I96,"*Đ4*")</f>
         <v/>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="26" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="26" t="inlineStr">
         <is>
           <t>Mục có liên quan Đ5</t>
         </is>
       </c>
-      <c r="B20" s="19">
+      <c r="B21" s="19">
         <f>COUNTIF('Ra soat (GAP)'!I2:I96,"*Đ5*")</f>
         <v/>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="26" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="26" t="inlineStr">
         <is>
           <t>Mục có liên quan Đ6</t>
         </is>
       </c>
-      <c r="B21" s="19">
+      <c r="B22" s="19">
         <f>COUNTIF('Ra soat (GAP)'!I2:I96,"*Đ6*")</f>
         <v/>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="27" t="inlineStr"/>
-      <c r="B22" s="19" t="n"/>
-    </row>
     <row r="23">
-      <c r="A23" s="25" t="inlineStr">
+      <c r="A23" s="27" t="inlineStr"/>
+      <c r="B23" s="19" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="25" t="inlineStr">
         <is>
           <t>CA ĐO 23/09/2026</t>
         </is>
       </c>
-      <c r="B23" s="19" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="26" t="inlineStr">
+      <c r="B24" s="19" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="26" t="inlineStr">
         <is>
           <t>Tổng ca</t>
         </is>
       </c>
-      <c r="B24" s="19">
+      <c r="B25" s="19">
         <f>COUNTA('Ca do 76 TC'!A2:A200)</f>
         <v/>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="26" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="26" t="inlineStr">
         <is>
           <t>Đạt</t>
         </is>
       </c>
-      <c r="B25" s="19">
+      <c r="B26" s="19">
         <f>COUNTIF('Ca do 76 TC'!F2:F200,"Đạt")</f>
         <v/>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="26" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="26" t="inlineStr">
         <is>
           <t>Không đạt</t>
         </is>
       </c>
-      <c r="B26" s="19">
+      <c r="B27" s="19">
         <f>COUNTIF('Ca do 76 TC'!F2:F200,"Không đạt")</f>
         <v/>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="26" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="26" t="inlineStr">
         <is>
           <t>Bị chặn</t>
         </is>
       </c>
-      <c r="B27" s="19">
+      <c r="B28" s="19">
         <f>COUNTIF('Ca do 76 TC'!F2:F200,"Bị chặn")</f>
         <v/>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="26" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="26" t="inlineStr">
         <is>
           <t>Bỏ qua</t>
         </is>
       </c>
-      <c r="B28" s="19">
+      <c r="B29" s="19">
         <f>COUNTIF('Ca do 76 TC'!F2:F200,"Bỏ qua")</f>
         <v/>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="26" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="26" t="inlineStr">
         <is>
           <t>Ca Đợt 1 nhắm tới (Đ1–Đ6)</t>
         </is>
       </c>
-      <c r="B29" s="19">
+      <c r="B30" s="19">
         <f>COUNTIF('Ca do 76 TC'!I2:I200,"Đợt 1")</f>
         <v/>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="26" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="26" t="inlineStr">
         <is>
           <t>Ca hồi quy phải giữ</t>
         </is>
       </c>
-      <c r="B30" s="19">
+      <c r="B31" s="19">
         <f>COUNTIF('Ca do 76 TC'!I2:I200,"Hồi quy — phải giữ")</f>
         <v/>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="27" t="inlineStr"/>
-      <c r="B31" s="19" t="n"/>
-    </row>
     <row r="32">
-      <c r="A32" s="25" t="inlineStr">
+      <c r="A32" s="27" t="inlineStr"/>
+      <c r="B32" s="19" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="25" t="inlineStr">
         <is>
           <t>MÃ NGUỒN (đo 24/09/2026)</t>
         </is>
       </c>
-      <c r="B32" s="19" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="26" t="inlineStr">
-        <is>
-          <t>Năng lực trong docs/spec/caps.json</t>
-        </is>
-      </c>
-      <c r="B33" s="19" t="n">
-        <v>246</v>
-      </c>
+      <c r="B33" s="19" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="26" t="inlineStr">
         <is>
-          <t>Năng lực đã hiện thực (@capability)</t>
+          <t>Năng lực trong docs/spec/caps.json</t>
         </is>
       </c>
       <c r="B34" s="19" t="n">
-        <v>213</v>
+        <v>246</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="26" t="inlineStr">
         <is>
-          <t>Năng lực chưa hiện thực</t>
+          <t>Năng lực đã hiện thực (@capability)</t>
         </is>
       </c>
       <c r="B35" s="19" t="n">
-        <v>33</v>
+        <v>213</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="26" t="inlineStr">
         <is>
-          <t>Mẫu chuỗi trong docs/spec/dialog/chains.json</t>
+          <t>Năng lực chưa hiện thực</t>
         </is>
       </c>
       <c r="B36" s="19" t="n">
-        <v>22</v>
+        <v>33</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="26" t="inlineStr">
         <is>
-          <t>Manifest ISA trong docs/spec/isa/</t>
+          <t>Mẫu chuỗi trong docs/spec/dialog/chains.json</t>
         </is>
       </c>
       <c r="B37" s="19" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="26" t="inlineStr">
         <is>
-          <t>Phương thức JSON-RPC trong openrpc.json</t>
+          <t>Manifest ISA trong docs/spec/isa/</t>
         </is>
       </c>
       <c r="B38" s="19" t="n">
-        <v>65</v>
+        <v>3</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="26" t="inlineStr">
         <is>
-          <t>Loại sự kiện sổ cái</t>
+          <t>Phương thức JSON-RPC trong openrpc.json</t>
         </is>
       </c>
       <c r="B39" s="19" t="n">
-        <v>24</v>
+        <v>65</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="26" t="inlineStr">
         <is>
-          <t>Tệp test trong tests/</t>
+          <t>Loại sự kiện sổ cái</t>
         </is>
       </c>
       <c r="B40" s="19" t="n">
-        <v>81</v>
+        <v>24</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="26" t="inlineStr">
         <is>
+          <t>Tệp test trong tests/</t>
+        </is>
+      </c>
+      <c r="B41" s="19" t="n">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="26" t="inlineStr">
+        <is>
           <t>Mục DEVIATIONS đã dùng</t>
         </is>
       </c>
-      <c r="B41" s="19" t="inlineStr">
-        <is>
-          <t>DEV-001 … DEV-233 (220–229 mâu thuẫn tài liệu, 230–233 từ Đ1)</t>
+      <c r="B42" s="19" t="inlineStr">
+        <is>
+          <t>DEV-001 … DEV-236 (220–229 mâu thuẫn tài liệu, 230–233 Đ1, 234–236 Đ2)</t>
         </is>
       </c>
     </row>

--- a/docs/v1.4/EIDE-GAP-35_Ra_soat_ma_v1.4.xlsx
+++ b/docs/v1.4/EIDE-GAP-35_Ra_soat_ma_v1.4.xlsx
@@ -837,12 +837,12 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>XONG Đ1 / XONG Đ2</t>
+          <t>XONG Đ1 / Đ2 / Đ3</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Đã hiện thực ngày 24/09/2026; cột cuối ghi tệp và BÀI KIỂM canh nó. `make check-py` xanh: ruff, 2011 test, check-spec, check-gen.</t>
+          <t>Đã hiện thực ngày 24/09/2026; cột cuối ghi tệp và BÀI KIỂM canh nó. `make check-py` xanh: ruff, 2038 test, check-spec, check-gen.</t>
         </is>
       </c>
     </row>
@@ -5293,9 +5293,9 @@
           <t>Manifest ISA đủ họ: armv6-m, armv7-m, armv7e-m, armv8-m, avr8, rv32imac, xtensa-lx6/lx7</t>
         </is>
       </c>
-      <c r="E72" s="11" t="inlineStr">
-        <is>
-          <t>KHÔNG</t>
+      <c r="E72" s="9" t="inlineStr">
+        <is>
+          <t>XONG Đ3</t>
         </is>
       </c>
       <c r="F72" s="7" t="inlineStr">
@@ -5333,7 +5333,11 @@
           <t>Việc rẻ nhất trong Đợt 1 — mở khoá TC018 mà không sửa mã.</t>
         </is>
       </c>
-      <c r="M72" s="7" t="inlineStr"/>
+      <c r="M72" s="7" t="inlineStr">
+        <is>
+          <t>docs/spec/isa/armv7-m.yaml (mới, sinh từ tgt_sim.js) + thu hẹp armv7e-m từ ^STM32F[2-4] xuống ^STM32F[34] — STM32F2 cũng là Cortex-M3 KHÔNG có FPU, để armv7e-m nhận nó là làm luật no_float_isr_without_fpu mất hiệu lực ([DEV-237]). STM32F103/F205/LPC17 → armv7-m. Canh bởi tests/test_de_nghi_ho_chieu.py::test_chip_ve_dung_isa, ::test_armv7e_m_khong_con_nhan_STM32F2, ::test_manifest_armv7_m_khai_du_phan_toolchain_va_khong_co_fpu</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="7" t="inlineStr">
@@ -5714,9 +5718,9 @@
           <t>search.web qua SearXNG cục bộ, truy vấn dựng bằng mã từ chips[], xếp hạng ưu tiên tên miền nhà sản xuất, tải chỉ sau G-DATA; mất mạng → E3xxx lỗi MẠNG (không phải lỗi tệp), lưu trạng thái, tiếp tục được</t>
         </is>
       </c>
-      <c r="E79" s="8" t="inlineStr">
-        <is>
-          <t>MỘT PHẦN</t>
+      <c r="E79" s="9" t="inlineStr">
+        <is>
+          <t>XONG Đ3</t>
         </is>
       </c>
       <c r="F79" s="7" t="inlineStr">
@@ -5750,7 +5754,11 @@
         </is>
       </c>
       <c r="L79" s="7" t="inlineStr"/>
-      <c r="M79" s="7" t="inlineStr"/>
+      <c r="M79" s="7" t="inlineStr">
+        <is>
+          <t>src/eide/caps/search.py::_loi_mang — tách E4005 NETWORK_FAILED (resumable) / E4004 TIMEOUT / E4000 TOOL_FAILED, trước đó gộp hết vào TIMEOUT. E4005 thêm vào errors.json TỪ NGUỒN (api.js) + sinh lại binding Swift. Câu lỗi nói thẳng "lỗi MẠNG, không phải lỗi tệp" (TC072). CHƯA làm: dựng SearXNG thật và doc.approve/G-DATA — chờ Đợt 2 (nền Fact). Canh bởi ::test_phan_loai_loi_mang, ::test_loi_mang_noi_ro_KHONG_phai_loi_tep, ::test_E4005_co_trong_dac_ta</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="7" t="inlineStr">
@@ -8110,9 +8118,9 @@
           <t>Đối chiếu ISA của chip với manifest; không khớp → nói thẳng thay vì đưa 3 lựa chọn đều sai</t>
         </is>
       </c>
-      <c r="D10" s="8" t="inlineStr">
-        <is>
-          <t>MỘT PHẦN</t>
+      <c r="D10" s="9" t="inlineStr">
+        <is>
+          <t>XONG Đ3</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
@@ -13958,7 +13966,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B42"/>
+  <dimension ref="A1:B44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -14051,329 +14059,350 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="27" t="inlineStr"/>
-      <c r="B9" s="19" t="n"/>
+      <c r="A9" s="26" t="inlineStr">
+        <is>
+          <t>XONG Đ3 (đã sửa 24/09/2026)</t>
+        </is>
+      </c>
+      <c r="B9" s="19">
+        <f>COUNTIF('Ra soat (GAP)'!E2:E96,"XONG Đ3")</f>
+        <v/>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="25" t="inlineStr">
+      <c r="A10" s="27" t="inlineStr"/>
+      <c r="B10" s="19" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="25" t="inlineStr">
         <is>
           <t>THEO ĐỢT</t>
         </is>
       </c>
-      <c r="B10" s="19" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="26" t="inlineStr">
+      <c r="B11" s="19" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="26" t="inlineStr">
         <is>
           <t>Đợt 1</t>
         </is>
       </c>
-      <c r="B11" s="19">
+      <c r="B12" s="19">
         <f>COUNTIF('Ra soat (GAP)'!J2:J96,"Đợt 1")</f>
         <v/>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="26" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="26" t="inlineStr">
         <is>
           <t>Đợt 2</t>
         </is>
       </c>
-      <c r="B12" s="19">
+      <c r="B13" s="19">
         <f>COUNTIF('Ra soat (GAP)'!J2:J96,"Đợt 2")</f>
         <v/>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="26" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="26" t="inlineStr">
         <is>
           <t>Đợt 3</t>
         </is>
       </c>
-      <c r="B13" s="19">
+      <c r="B14" s="19">
         <f>COUNTIF('Ra soat (GAP)'!J2:J96,"Đợt 3")</f>
         <v/>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="26" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="26" t="inlineStr">
         <is>
           <t>Đợt 4</t>
         </is>
       </c>
-      <c r="B14" s="19">
+      <c r="B15" s="19">
         <f>COUNTIF('Ra soat (GAP)'!J2:J96,"Đợt 4")</f>
         <v/>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="27" t="inlineStr"/>
-      <c r="B15" s="19" t="n"/>
-    </row>
     <row r="16">
-      <c r="A16" s="25" t="inlineStr">
+      <c r="A16" s="27" t="inlineStr"/>
+      <c r="B16" s="19" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="25" t="inlineStr">
         <is>
           <t>THEO SỬA ĐỔI (Đợt 1)</t>
         </is>
       </c>
-      <c r="B16" s="19" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="26" t="inlineStr">
+      <c r="B17" s="19" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="26" t="inlineStr">
         <is>
           <t>Mục có liên quan Đ1</t>
         </is>
       </c>
-      <c r="B17" s="19">
+      <c r="B18" s="19">
         <f>COUNTIF('Ra soat (GAP)'!I2:I96,"*Đ1*")</f>
         <v/>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="26" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="26" t="inlineStr">
         <is>
           <t>Mục có liên quan Đ2</t>
         </is>
       </c>
-      <c r="B18" s="19">
+      <c r="B19" s="19">
         <f>COUNTIF('Ra soat (GAP)'!I2:I96,"*Đ2*")</f>
         <v/>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="26" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="26" t="inlineStr">
         <is>
           <t>Mục có liên quan Đ3</t>
         </is>
       </c>
-      <c r="B19" s="19">
+      <c r="B20" s="19">
         <f>COUNTIF('Ra soat (GAP)'!I2:I96,"*Đ3*")</f>
         <v/>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="26" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="26" t="inlineStr">
         <is>
           <t>Mục có liên quan Đ4</t>
         </is>
       </c>
-      <c r="B20" s="19">
+      <c r="B21" s="19">
         <f>COUNTIF('Ra soat (GAP)'!I2:I96,"*Đ4*")</f>
         <v/>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="26" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="26" t="inlineStr">
         <is>
           <t>Mục có liên quan Đ5</t>
         </is>
       </c>
-      <c r="B21" s="19">
+      <c r="B22" s="19">
         <f>COUNTIF('Ra soat (GAP)'!I2:I96,"*Đ5*")</f>
         <v/>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="26" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="26" t="inlineStr">
         <is>
           <t>Mục có liên quan Đ6</t>
         </is>
       </c>
-      <c r="B22" s="19">
+      <c r="B23" s="19">
         <f>COUNTIF('Ra soat (GAP)'!I2:I96,"*Đ6*")</f>
         <v/>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="27" t="inlineStr"/>
-      <c r="B23" s="19" t="n"/>
-    </row>
     <row r="24">
-      <c r="A24" s="25" t="inlineStr">
+      <c r="A24" s="27" t="inlineStr"/>
+      <c r="B24" s="19" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="25" t="inlineStr">
         <is>
           <t>CA ĐO 23/09/2026</t>
         </is>
       </c>
-      <c r="B24" s="19" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="26" t="inlineStr">
+      <c r="B25" s="19" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="26" t="inlineStr">
         <is>
           <t>Tổng ca</t>
         </is>
       </c>
-      <c r="B25" s="19">
+      <c r="B26" s="19">
         <f>COUNTA('Ca do 76 TC'!A2:A200)</f>
         <v/>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="26" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="26" t="inlineStr">
         <is>
           <t>Đạt</t>
         </is>
       </c>
-      <c r="B26" s="19">
+      <c r="B27" s="19">
         <f>COUNTIF('Ca do 76 TC'!F2:F200,"Đạt")</f>
         <v/>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="26" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="26" t="inlineStr">
         <is>
           <t>Không đạt</t>
         </is>
       </c>
-      <c r="B27" s="19">
+      <c r="B28" s="19">
         <f>COUNTIF('Ca do 76 TC'!F2:F200,"Không đạt")</f>
         <v/>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="26" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="26" t="inlineStr">
         <is>
           <t>Bị chặn</t>
         </is>
       </c>
-      <c r="B28" s="19">
+      <c r="B29" s="19">
         <f>COUNTIF('Ca do 76 TC'!F2:F200,"Bị chặn")</f>
         <v/>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="26" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="26" t="inlineStr">
         <is>
           <t>Bỏ qua</t>
         </is>
       </c>
-      <c r="B29" s="19">
+      <c r="B30" s="19">
         <f>COUNTIF('Ca do 76 TC'!F2:F200,"Bỏ qua")</f>
         <v/>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="26" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="26" t="inlineStr">
         <is>
           <t>Ca Đợt 1 nhắm tới (Đ1–Đ6)</t>
         </is>
       </c>
-      <c r="B30" s="19">
+      <c r="B31" s="19">
         <f>COUNTIF('Ca do 76 TC'!I2:I200,"Đợt 1")</f>
         <v/>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="26" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="26" t="inlineStr">
         <is>
           <t>Ca hồi quy phải giữ</t>
         </is>
       </c>
-      <c r="B31" s="19">
+      <c r="B32" s="19">
         <f>COUNTIF('Ca do 76 TC'!I2:I200,"Hồi quy — phải giữ")</f>
         <v/>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="27" t="inlineStr"/>
-      <c r="B32" s="19" t="n"/>
-    </row>
     <row r="33">
-      <c r="A33" s="25" t="inlineStr">
+      <c r="A33" s="27" t="inlineStr"/>
+      <c r="B33" s="19" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="25" t="inlineStr">
         <is>
           <t>MÃ NGUỒN (đo 24/09/2026)</t>
         </is>
       </c>
-      <c r="B33" s="19" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="26" t="inlineStr">
-        <is>
-          <t>Năng lực trong docs/spec/caps.json</t>
-        </is>
-      </c>
-      <c r="B34" s="19" t="n">
-        <v>246</v>
-      </c>
+      <c r="B34" s="19" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="26" t="inlineStr">
         <is>
-          <t>Năng lực đã hiện thực (@capability)</t>
+          <t>Năng lực trong docs/spec/caps.json</t>
         </is>
       </c>
       <c r="B35" s="19" t="n">
-        <v>213</v>
+        <v>246</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="26" t="inlineStr">
         <is>
-          <t>Năng lực chưa hiện thực</t>
+          <t>Năng lực đã hiện thực (@capability)</t>
         </is>
       </c>
       <c r="B36" s="19" t="n">
-        <v>33</v>
+        <v>213</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="26" t="inlineStr">
         <is>
-          <t>Mẫu chuỗi trong docs/spec/dialog/chains.json</t>
+          <t>Năng lực chưa hiện thực</t>
         </is>
       </c>
       <c r="B37" s="19" t="n">
-        <v>22</v>
+        <v>33</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="26" t="inlineStr">
         <is>
-          <t>Manifest ISA trong docs/spec/isa/</t>
+          <t>Mẫu chuỗi trong docs/spec/dialog/chains.json</t>
         </is>
       </c>
       <c r="B38" s="19" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="26" t="inlineStr">
         <is>
-          <t>Phương thức JSON-RPC trong openrpc.json</t>
+          <t>Manifest ISA trong docs/spec/isa/</t>
         </is>
       </c>
       <c r="B39" s="19" t="n">
-        <v>65</v>
+        <v>4</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="26" t="inlineStr">
         <is>
-          <t>Loại sự kiện sổ cái</t>
+          <t>Phương thức JSON-RPC trong openrpc.json</t>
         </is>
       </c>
       <c r="B40" s="19" t="n">
-        <v>24</v>
+        <v>65</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="26" t="inlineStr">
         <is>
-          <t>Tệp test trong tests/</t>
+          <t>Loại sự kiện sổ cái</t>
         </is>
       </c>
       <c r="B41" s="19" t="n">
-        <v>83</v>
+        <v>24</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="26" t="inlineStr">
         <is>
+          <t>Mã lỗi trong errors.json</t>
+        </is>
+      </c>
+      <c r="B42" s="19" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="26" t="inlineStr">
+        <is>
+          <t>Tệp test trong tests/</t>
+        </is>
+      </c>
+      <c r="B43" s="19" t="n">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="26" t="inlineStr">
+        <is>
           <t>Mục DEVIATIONS đã dùng</t>
         </is>
       </c>
-      <c r="B42" s="19" t="inlineStr">
-        <is>
-          <t>DEV-001 … DEV-236 (220–229 mâu thuẫn tài liệu, 230–233 Đ1, 234–236 Đ2)</t>
+      <c r="B44" s="19" t="inlineStr">
+        <is>
+          <t>DEV-001 … DEV-240 (220–229 mâu thuẫn tài liệu, 230–233 Đ1, 234–236 Đ2, 237–240 Đ3)</t>
         </is>
       </c>
     </row>
